--- a/data/export/2026-09-23-operations.xlsx
+++ b/data/export/2026-09-23-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -648,24 +648,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -896,29 +896,29 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1149,26 +1149,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 35分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1176,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1200,12 +1196,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1215,22 +1211,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1273,24 +1269,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>07:20采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1300,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1393,26 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1464,13 +1464,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1483,24 +1487,24 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1513,34 +1517,34 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±10分钟</t>
+          <t>07:20采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±13分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1554,7 +1558,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1564,12 +1568,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1589,40 +1593,40 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1637,34 +1641,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数125分钟，约±13分钟</t>
+          <t>07:20采样：该车到重点站新川路妙境路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1682,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1688,7 +1692,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1713,40 +1717,40 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1761,24 +1765,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±12分钟</t>
+          <t>07:20采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1802,7 +1806,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1812,7 +1816,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1837,40 +1841,40 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1885,24 +1889,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1926,7 +1930,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1936,7 +1940,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1961,40 +1965,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2009,22 +2013,26 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2032,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2046,7 +2054,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2056,61 +2064,65 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2125,30 +2137,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2162,7 +2178,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2172,17 +2188,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2192,41 +2208,45 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2241,30 +2261,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2278,7 +2302,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2288,17 +2312,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2308,41 +2332,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2357,19 +2385,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±6分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2384,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2398,7 +2426,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2423,50 +2451,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2481,34 +2509,34 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±6分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2522,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2547,40 +2575,40 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2590,7 +2618,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2605,30 +2633,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 88分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2652,17 +2684,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,41 +2704,45 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2721,34 +2757,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±14分钟</t>
+          <t>07:19采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2762,7 +2798,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2772,12 +2808,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2797,40 +2833,40 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2845,30 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2882,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2892,17 +2932,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2912,41 +2952,45 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2961,34 +3005,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±8分钟</t>
+          <t>07:19采样：该车到重点站沪南路高科西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3002,47 +3046,3715 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>07:11采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>174分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>172分钟</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数166分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>162分钟</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数162分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:19采样，终点ETA 34分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>114分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:19采样，终点ETA 60分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>107分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站金高路行泰路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站巨峰路五莲路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>06:50</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站杨高北路（外高桥保税区南站） ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站杨高北路花山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>95.0</t>
         </is>
       </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>2/4</t>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-operations.xlsx
+++ b/data/export/2026-09-23-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1154,17 +1154,21 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,12 +1200,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1221,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1268,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1296,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1320,12 +1324,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1335,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1388,29 +1392,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,12 +1448,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1459,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1516,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±13分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1583,22 +1587,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1636,29 +1640,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站新川路妙境路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,12 +1696,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1707,22 +1711,22 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1764,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1792,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1816,12 +1820,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1831,22 +1835,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1889,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1965,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2013,24 +2017,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2089,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2137,24 +2141,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,12 +2192,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2213,12 +2217,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2261,24 +2265,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2312,12 +2316,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2337,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2385,24 +2389,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±6分钟</t>
+          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2412,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2441,7 +2445,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2461,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2479,24 +2483,24 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2509,24 +2513,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2536,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2550,7 +2554,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2585,40 +2589,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2633,24 +2637,24 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
+          <t>08:22采样：该车到重点站新川路华东路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2674,7 +2678,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2699,50 +2703,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2757,24 +2761,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±10分钟</t>
+          <t>08:22采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2784,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2798,7 +2802,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2823,50 +2827,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2881,34 +2885,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±15分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2922,7 +2926,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2932,12 +2936,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2957,40 +2961,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3005,19 +3009,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路高科西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3027,12 +3031,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3046,7 +3050,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3061,7 +3065,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3071,50 +3075,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3129,22 +3133,26 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3166,7 +3174,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3176,61 +3184,65 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3263,12 +3275,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3282,7 +3294,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3307,46 +3319,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3361,24 +3377,24 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3388,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3402,7 +3418,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3412,12 +3428,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3427,50 +3443,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3485,34 +3501,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>07:11采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±11分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3526,7 +3542,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3536,12 +3552,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3551,22 +3567,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3579,24 +3595,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3604,39 +3620,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3650,7 +3666,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3660,12 +3676,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3675,22 +3691,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3703,24 +3719,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3728,39 +3744,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3774,7 +3790,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3784,12 +3800,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3799,22 +3815,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3827,24 +3843,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3857,34 +3873,34 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±12分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3898,7 +3914,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3908,7 +3924,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3933,12 +3949,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3967,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3961,7 +3977,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3981,30 +3997,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 49分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4018,7 +4034,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4033,7 +4049,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4043,18 +4059,22 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4087,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4077,7 +4097,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4087,44 +4107,40 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4132,13 +4148,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4148,17 +4180,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4168,17 +4200,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4191,24 +4219,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4221,34 +4249,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数166分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4262,7 +4286,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4272,17 +4296,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4292,17 +4316,13 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4335,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4325,7 +4345,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4345,30 +4365,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4382,7 +4406,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4392,17 +4416,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4412,13 +4436,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4459,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4441,7 +4469,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4461,19 +4489,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数162分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4483,12 +4511,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4502,7 +4530,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4517,7 +4545,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4537,12 +4565,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4583,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4565,7 +4593,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4585,34 +4613,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>08:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4626,7 +4654,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4641,7 +4669,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4661,12 +4689,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4707,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4689,7 +4717,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4709,34 +4737,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4750,7 +4778,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4760,12 +4788,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4785,40 +4813,40 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4833,30 +4861,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:19采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4870,7 +4902,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4880,12 +4912,12 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4895,50 +4927,50 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4953,30 +4985,30 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:19采样，终点ETA 60分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4990,7 +5022,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5005,7 +5037,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5026,35 +5058,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5069,34 +5101,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站金高路行泰路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5110,7 +5142,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5145,40 +5177,40 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5193,34 +5225,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站巨峰路五莲路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5234,7 +5266,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5244,7 +5276,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5269,40 +5301,40 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5317,34 +5349,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5358,7 +5386,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5368,17 +5396,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5388,45 +5416,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5441,34 +5465,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站杨高北路（外高桥保税区南站） ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±6分钟</t>
+          <t>08:21采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5482,7 +5506,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5492,7 +5516,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5517,40 +5541,40 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5565,34 +5589,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站杨高北路花山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5606,7 +5630,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5641,40 +5665,40 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5689,34 +5713,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5730,7 +5754,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5765,40 +5789,40 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5813,34 +5837,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5854,7 +5878,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5864,12 +5888,12 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5889,40 +5913,40 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5937,34 +5961,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>08:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5978,7 +6002,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5988,12 +6012,12 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6013,40 +6037,40 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6061,34 +6085,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±15分钟</t>
+          <t>08:11采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6102,7 +6126,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6112,12 +6136,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -6137,40 +6161,40 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6185,34 +6209,34 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6226,7 +6250,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6241,7 +6265,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6261,40 +6285,40 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6309,30 +6333,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数148分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6346,7 +6374,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6356,17 +6384,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6376,41 +6404,45 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6425,34 +6457,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±12分钟</t>
+          <t>08:21采样：该车到重点站浦东大道东波路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6466,7 +6498,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6476,12 +6508,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6501,40 +6533,40 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6549,34 +6581,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站川周公路康沈路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6590,7 +6622,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6605,7 +6637,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6625,40 +6657,40 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6673,34 +6705,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±12分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6714,47 +6746,3731 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>154分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>110分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站云山路灵山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>107分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>106分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>07:40采样：该车到重点站花山路大同路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站金高路东靖路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站云山路灵山路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数108分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="AD51" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-operations.xlsx
+++ b/data/export/2026-09-23-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7536,17 +7536,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8652,17 +8652,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10748,17 +10748,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11417,24 +11417,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11655,32 +11655,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11688,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11712,17 +11716,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11732,17 +11736,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11812,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11895,32 +11899,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11928,7 +11936,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11952,17 +11960,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11972,12 +11980,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12015,32 +12023,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12048,7 +12060,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12072,17 +12084,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12092,12 +12104,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12168,7 +12180,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12288,7 +12300,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12412,7 +12424,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12456,17 +12468,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -12590,7 +12602,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12726,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13048,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13090,7 +13102,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13226,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13350,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13474,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13544,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13586,7 +13598,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13664,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -14032,7 +14044,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14076,17 +14088,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14164,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14292,7 +14304,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14346,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -14656,7 +14668,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14700,17 +14712,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -14776,7 +14788,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14900,7 +14912,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14954,7 +14966,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15214,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15400,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15512,7 +15524,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15556,12 +15568,12 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
@@ -15760,7 +15772,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15938,7 +15950,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16016,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16048,17 +16060,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16314,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16516,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16558,7 +16570,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16694,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16814,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16938,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -16996,7 +17008,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17050,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17368,7 +17380,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17412,17 +17424,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -17492,7 +17504,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17546,7 +17558,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17752,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17784,17 +17796,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -17988,7 +18000,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18112,7 +18124,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18166,7 +18178,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18372,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18608,7 +18620,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18910,7 +18922,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19046,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -19154,7 +19166,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19232,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19604,7 +19616,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -20100,7 +20112,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20154,7 +20166,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20662,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20786,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20906,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21212,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21378,7 +21390,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -21448,7 +21460,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21492,17 +21504,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -21572,7 +21584,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21616,12 +21628,12 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
@@ -21692,7 +21704,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21812,7 +21824,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21936,7 +21948,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21980,17 +21992,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22072,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22104,17 +22116,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22196,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22308,7 +22320,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22432,7 +22444,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22486,7 +22498,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22568,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22610,7 +22622,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22746,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -22858,7 +22870,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -23176,7 +23188,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23230,7 +23242,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23478,7 +23490,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23738,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23928,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24094,7 +24106,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -24160,7 +24172,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24243,32 +24255,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24276,7 +24292,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24300,17 +24316,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24320,12 +24336,12 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
@@ -24396,7 +24412,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24488,7 +24504,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24516,7 +24532,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24619,32 +24635,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24652,7 +24672,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24676,17 +24696,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24696,17 +24716,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -24739,32 +24759,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24772,7 +24796,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24796,17 +24820,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24816,17 +24840,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24916,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24979,12 +25003,12 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -25012,7 +25036,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25020,10 +25044,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R199" s="2" t="inlineStr"/>
-      <c r="S199" s="2" t="inlineStr"/>
-      <c r="T199" s="2" t="inlineStr"/>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V199" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -25132,7 +25172,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25186,7 +25226,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -25219,32 +25259,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25252,7 +25296,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25276,17 +25320,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25296,17 +25340,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25416,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25426,7 +25470,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25536,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25546,7 +25590,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -25612,7 +25656,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25666,7 +25710,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -25732,7 +25776,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25852,7 +25896,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25896,17 +25940,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26270,7 +26314,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -26460,7 +26504,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26638,7 +26682,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26828,7 +26872,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26877,12 +26921,12 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26952,7 +26996,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -26996,17 +27040,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27174,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27374,7 +27418,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27542,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -27622,7 +27666,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27812,7 +27856,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27856,17 +27900,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27932,7 +27976,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27976,17 +28020,17 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28106,7 +28150,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -28474,7 +28518,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28792,7 +28836,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28916,7 +28960,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28960,17 +29004,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29094,7 +29138,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29204,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29209,12 +29253,12 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29378,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29582,7 +29626,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29750,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29776,7 +29820,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29820,17 +29864,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30400,7 +30444,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30456,17 +30500,17 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30714,7 +30758,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30882,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -30962,7 +31006,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31254,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31582,7 +31626,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31874,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31998,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32122,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32644,7 +32688,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32688,17 +32732,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32822,7 +32866,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32946,7 +32990,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33114,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -33194,7 +33238,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -33264,7 +33308,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33512,7 +33556,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33561,12 +33605,12 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33814,7 +33858,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34008,7 +34052,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34052,17 +34096,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34132,7 +34176,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34176,17 +34220,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34504,7 +34548,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34548,17 +34592,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34850,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34930,7 +34974,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -35054,7 +35098,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35124,7 +35168,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35302,7 +35346,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -35372,7 +35416,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35421,12 +35465,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35674,7 +35718,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35912,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35912,17 +35956,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36276,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36276,17 +36320,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36604,7 +36648,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36648,17 +36692,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36782,7 +36826,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -36906,7 +36950,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -37100,7 +37144,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37321,24 +37365,24 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -37348,7 +37392,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37397,12 +37441,12 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37435,32 +37479,36 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37468,7 +37516,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37492,17 +37540,17 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -37512,17 +37560,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37555,32 +37603,36 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -37588,7 +37640,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37612,17 +37664,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37632,17 +37684,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37675,32 +37727,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -37708,7 +37764,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37732,17 +37788,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37752,17 +37808,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37828,7 +37884,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37948,7 +38004,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37997,12 +38053,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38124,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38112,17 +38168,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
